--- a/portfolio/public/Portfolio_2.xlsx
+++ b/portfolio/public/Portfolio_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Portfolio\portfolio\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40292DC7-F8F2-42F6-AD1D-F69581C1DE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2377D3F-AB67-4B28-9C32-9F106EC2B79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
@@ -1650,6 +1650,146 @@
     </r>
   </si>
   <si>
+    <t>Fire &amp; Smoke Detection System</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">A real-time computer vision system that detects </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>fire and smoke</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve"> from images, videos, and camera streams. The system uses object detection to identify hazards, display bounding boxes and confidence scores, and provide an interactive interface for monitoring and testing.
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Marwan Allam - Abd Al-Kareem Ahmed - Ahmed Arafat
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python · YOLOv8 · OpenCV · Roboflow · Streamlit · Ultralytics
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Worked as a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Computer Vision / AI Developer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve"> on the detection system.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Prepared and worked with the fire and smoke dataset, including augmentation and preprocessing.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Trained and evaluated the YOLOv8 detection model.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Tuned training parameters and confidence thresholds to improve detection performance.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Achieved approximately </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>82% detection accuracy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve"> on the project evaluation.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>AI Proactive Road Safety System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <u/>
@@ -1657,148 +1797,90 @@
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>https://youtube.com/shorts/j3ALV9pQepQ?si=mFUJa_f3i8M7FJO3</t>
-    </r>
-  </si>
-  <si>
-    <t>Fire &amp; Smoke Detection System</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">A real-time computer vision system that detects </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>fire and smoke</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve"> from images, videos, and camera streams. The system uses object detection to identify hazards, display bounding boxes and confidence scores, and provide an interactive interface for monitoring and testing.
-</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Marwan Allam - Abd Al-Kareem Ahmed - Ahmed Arafat
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python · YOLOv8 · OpenCV · Roboflow · Streamlit · Ultralytics
-</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Worked as a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Computer Vision / AI Developer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve"> on the detection system.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Prepared and worked with the fire and smoke dataset, including augmentation and preprocessing.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Trained and evaluated the YOLOv8 detection model.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Tuned training parameters and confidence thresholds to improve detection performance.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Achieved approximately </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>82% detection accuracy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve"> on the project evaluation.
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>AI Proactive Road Safety System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
+      <t>https://github.com/Basant-Tarik01/AI-Proactive-Road-Safety-System</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">An AI-powered road safety project developed to identify potential road risks proactively and support accident prevention before dangerous situations occur. The system combines AI-based analysis with a safety-focused workflow to transform detected risks into actionable warnings.
+</t>
+  </si>
+  <si>
+    <t>Python · Machine Learning · Computer Vision · AI ·</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Contributed to understanding and analyzing the road-safety problem.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Applied machine learning and AI concepts to a real-world safety problem.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Contributed to building a proactive approach that focuses on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>risk detection before accidents happen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Developed the project as part of the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>DEPI AI &amp; Data Science — Microsoft Machine Learning Engineer track</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Flight Delay Prediction &amp; MLOps System</t>
   </si>
   <si>
     <r>
@@ -1808,121 +1890,28 @@
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
       </rPr>
-      <t>https://github.com/Basant-Tarik01/AI-Proactive-Road-Safety-System</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">An AI-powered road safety project developed to identify potential road risks proactively and support accident prevention before dangerous situations occur. The system combines AI-based analysis with a safety-focused workflow to transform detected risks into actionable warnings.
-</t>
-  </si>
-  <si>
-    <t>Python · Machine Learning · Computer Vision · AI ·</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Contributed to understanding and analyzing the road-safety problem.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Applied machine learning and AI concepts to a real-world safety problem.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Contributed to building a proactive approach that focuses on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>risk detection before accidents happen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Developed the project as part of the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>DEPI AI &amp; Data Science — Microsoft Machine Learning Engineer track</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-  </si>
-  <si>
-    <t>Flight Delay Prediction &amp; MLOps System</t>
-  </si>
-  <si>
+      <t>https://github.com/Aly-EL-Badry/Flight-Delay-Prediction-MLops</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">An end-to-end machine learning system that predicts flight delays using historical flight data. The project covers data preprocessing, model development, experiment tracking, pipeline orchestration, API deployment, and integration with a frontend
+</t>
+  </si>
+  <si>
+    <t>Aly El-Badry - Rawan Ahmed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Python · TensorFlow · Deep Learning · ZenML · MLflow · FastAPI · Docker · React · Tailwind CSS · Vercel · </t>
+    </r>
     <r>
       <rPr>
         <u/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Helvetica Neue"/>
-      </rPr>
-      <t>https://github.com/Aly-EL-Badry/Flight-Delay-Prediction-MLops</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">An end-to-end machine learning system that predicts flight delays using historical flight data. The project covers data preprocessing, model development, experiment tracking, pipeline orchestration, API deployment, and integration with a frontend
-</t>
-  </si>
-  <si>
-    <t>Aly El-Badry - Rawan Ahmed</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Python · TensorFlow · Deep Learning · ZenML · MLflow · FastAPI · Docker · React · Tailwind CSS · Vercel · </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Times New Roman"/>
@@ -2016,91 +2005,6 @@
         <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve"> to expose the trained model as an API.
-</t>
-    </r>
-  </si>
-  <si>
-    <t>Face Recognition System</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Helvetica Neue"/>
-      </rPr>
-      <t>https://github.com/heba10allah/GTC-Final-project</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">A face recognition application that identifies and classifies faces using deep face embeddings. The system uses a pretrained FaceNet-based architecture and provides an interactive interface for face recognition through uploaded images and camera input.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python · FaceNet · InceptionResnetV1 · VGGFace2 · PyTorch · Kaggle · Streamlit · OpenCV · Pickle
-</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Took responsibility for the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>deployment and application integration</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Integrated the trained face-recognition model into the application.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Built the Streamlit interface for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>image upload and camera-based recognition</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">.
 </t>
     </r>
   </si>
@@ -3080,12 +2984,41 @@
   <si>
     <t>https://res.cloudinary.com/lrmifkhy/image/upload/v1790888074/Screenshot_2026-10-01_214658.png</t>
   </si>
+  <si>
+    <t>https://res.cloudinary.com/lrmifkhy/image/upload/v1790962016/Screenshot_2026-02-05_213653.png
+https://res.cloudinary.com/lrmifkhy/image/upload/v1790962016/Screenshot_2026-02-05_213711.png
+https://res.cloudinary.com/lrmifkhy/image/upload/v1790962015/Screenshot_2026-02-05_213701.png
+https://res.cloudinary.com/lrmifkhy/image/upload/v1790962014/Screenshot_2026-02-05_213642.png
+https://res.cloudinary.com/lrmifkhy/image/upload/v1790962014/Screenshot_2026-02-05_213630.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/lrmifkhy/image/upload/v1790961981/Screenshot_2025-09-16_233646.png
+https://res.cloudinary.com/lrmifkhy/image/upload/v1790961928/Screenshot_2025-09-16_233631.png
+https://res.cloudinary.com/lrmifkhy/image/upload/v1790961928/Screenshot_2025-09-16_233609.png
+https://res.cloudinary.com/lrmifkhy/image/upload/v1790961918/Screenshot_2025-09-16_233555.png</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/lrmifkhy/image/upload/v1791004114/Screenshot_2026-10-02_195646.png
+https://drive.google.com/file/d/1ausrHsaXKfPh5tUXvwsh8kzJl3aHxnrz/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/lrmifkhy/image/upload/v1791004112/Screenshot_2026-10-02_160949.png
+https://drive.google.com/file/d/1mO2cMR-gfMHcbr8kakH-QgDdigvehuoE/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/lrmifkhy/image/upload/v1791004112/Screenshot_2026-10-02_203257.png
+https://youtube.com/shorts/j3ALV9pQepQ?si=mFUJa_f3i8M7FJO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://res.cloudinary.com/lrmifkhy/image/upload/v1791004111/Screenshot_2026-10-02_194514.png
+https://drive.google.com/file/d/1yp7JmABE26Xf_Iso1hsYKEF81qJo1ypg/view?usp=sharing </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -3152,6 +3085,18 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Inherit"/>
     </font>
   </fonts>
   <fills count="7">
@@ -3374,7 +3319,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3507,16 +3452,25 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4655,11 +4609,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" ht="49.95" customHeight="1">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
     </row>
     <row r="7" spans="2:4" ht="17.399999999999999">
       <c r="B7" s="1" t="s">
@@ -4706,7 +4660,7 @@
     </row>
     <row r="13" spans="2:4" ht="15">
       <c r="B13" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -4717,12 +4671,12 @@
         <v>5</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="15">
       <c r="B15" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -4733,7 +4687,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -4766,17 +4720,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.6" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
     </row>
     <row r="2" spans="1:9" ht="20.85" customHeight="1">
       <c r="A2" s="6"/>
@@ -5243,7 +5197,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="16.33203125" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="16.33203125" style="5" customWidth="1"/>
@@ -5255,19 +5209,19 @@
     <col min="10" max="16384" width="16.33203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.6" customHeight="1">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
     </row>
-    <row r="2" spans="1:8" ht="20.25" customHeight="1">
+    <row r="2" spans="1:10" ht="20.25" customHeight="1">
       <c r="A2" s="29" t="s">
         <v>92</v>
       </c>
@@ -5293,7 +5247,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="112.95" customHeight="1">
+    <row r="3" spans="1:10" ht="112.95" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>100</v>
       </c>
@@ -5314,104 +5268,116 @@
         <v>105</v>
       </c>
       <c r="H3" s="14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="127.8" customHeight="1">
+      <c r="A4" s="17" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="127.8" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>107</v>
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="21"/>
       <c r="D4" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="G4" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="H4" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="124.8" customHeight="1">
+      <c r="A5" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="H4" s="21"/>
-    </row>
-    <row r="5" spans="1:8" ht="124.8" customHeight="1">
-      <c r="A5" s="32" t="s">
+      <c r="B5" s="33" t="s">
         <v>112</v>
-      </c>
-      <c r="B5" s="33" t="s">
-        <v>113</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="H5" s="45" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="109.8" customHeight="1">
+      <c r="A6" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="21"/>
-    </row>
-    <row r="6" spans="1:8" ht="109.8" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="B6" s="33" t="s">
         <v>117</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>118</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="F6" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="G6" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="H6" s="45" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="97.8" customHeight="1">
+      <c r="A7" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="H6" s="21"/>
-    </row>
-    <row r="7" spans="1:8" ht="109.8" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="B7" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="C7" s="21"/>
+      <c r="D7" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="19" t="s">
+      <c r="E7" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="21"/>
       <c r="F7" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="H7" s="21"/>
+      <c r="H7" s="45" t="s">
+        <v>184</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" ht="97.8" customHeight="1">
+    <row r="8" spans="1:10" ht="112.8" customHeight="1">
       <c r="A8" s="35" t="s">
         <v>128</v>
       </c>
       <c r="B8" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="C8" s="21"/>
+      <c r="C8" s="20" t="s">
+        <v>130</v>
+      </c>
       <c r="D8" s="34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>132</v>
@@ -5419,31 +5385,14 @@
       <c r="G8" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="H8" s="21"/>
+      <c r="H8" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
     </row>
-    <row r="9" spans="1:8" ht="112.8" customHeight="1">
-      <c r="A9" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="H9" s="21"/>
+    <row r="9" spans="1:10" ht="19.95" customHeight="1">
+      <c r="H9" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5451,14 +5400,16 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="H3" r:id="rId2" display="https://youtube.com/shorts/j3ALV9pQepQ?si=mFUJa_f3i8M7FJO3" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
     <hyperlink ref="B5" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
     <hyperlink ref="B6" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
     <hyperlink ref="F6" r:id="rId5" display="fly.io" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="B9" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="C9" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="C8" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="H7" r:id="rId9" display="https://drive.google.com/file/d/1yp7JmABE26Xf_Iso1hsYKEF81qJo1ypg/view?usp=sharing " xr:uid="{AD7B3281-97E5-4EE2-922D-CB83E4285CFE}"/>
+    <hyperlink ref="H5" r:id="rId10" display="https://drive.google.com/file/d/1ausrHsaXKfPh5tUXvwsh8kzJl3aHxnrz/view?usp=sharing" xr:uid="{8BBD158E-7480-413D-9C78-6B0F19C36D1A}"/>
+    <hyperlink ref="H6" r:id="rId11" display="https://res.cloudinary.com/lrmifkhy/image/upload/v1790962016/Screenshot_2026-02-05_213653.png" xr:uid="{2110145D-85CB-4C4B-B9B5-956852F84B1E}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -5481,56 +5432,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.6" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
     </row>
     <row r="2" spans="1:5" ht="20.25" customHeight="1">
       <c r="A2" s="29" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C2" s="29" t="s">
         <v>95</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E2" s="37"/>
     </row>
     <row r="3" spans="1:5" ht="214.95" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>184</v>
+        <v>139</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>178</v>
       </c>
       <c r="E3" s="15"/>
     </row>
     <row r="4" spans="1:5" ht="304.8" customHeight="1">
       <c r="A4" s="32" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>183</v>
+        <v>142</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>177</v>
       </c>
       <c r="E4" s="21"/>
     </row>
@@ -5565,128 +5516,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.6" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
     </row>
     <row r="2" spans="1:6" ht="20.25" customHeight="1">
       <c r="A2" s="29" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F2" s="29" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="301.95" customHeight="1">
       <c r="A3" s="40" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E3" s="41" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="271.8" customHeight="1">
       <c r="A4" s="32" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="301.8" customHeight="1">
       <c r="A5" s="32" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="406.8" customHeight="1">
       <c r="A6" s="32" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F6" s="21"/>
     </row>
     <row r="7" spans="1:6" ht="409.6" customHeight="1">
       <c r="A7" s="32" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F7" s="21"/>
     </row>

--- a/portfolio/public/Portfolio_2.xlsx
+++ b/portfolio/public/Portfolio_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Portfolio\portfolio\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2377D3F-AB67-4B28-9C32-9F106EC2B79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89796268-A5CC-40C7-B969-D53CC326BD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="184">
   <si>
     <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -2499,9 +2499,6 @@
     <t>Generative Technology Center (GTC)</t>
   </si>
   <si>
-    <t>31 Aug 2025-26 Sep2025</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -2830,9 +2827,6 @@
   </si>
   <si>
     <t>EAEA — Egyptian Atomic Energy Authority</t>
-  </si>
-  <si>
-    <t>2 Aug 2026- 13 Aug 2026</t>
   </si>
   <si>
     <r>
@@ -3012,6 +3006,9 @@
   <si>
     <t xml:space="preserve">https://res.cloudinary.com/lrmifkhy/image/upload/v1791004111/Screenshot_2026-10-02_194514.png
 https://drive.google.com/file/d/1yp7JmABE26Xf_Iso1hsYKEF81qJo1ypg/view?usp=sharing </t>
+  </si>
+  <si>
+    <t>Aug 2026-Sep 2026</t>
   </si>
 </sst>
 </file>
@@ -5268,7 +5265,7 @@
         <v>105</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="127.8" customHeight="1">
@@ -5290,7 +5287,7 @@
         <v>110</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="124.8" customHeight="1">
@@ -5312,7 +5309,7 @@
         <v>115</v>
       </c>
       <c r="H5" s="45" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="109.8" customHeight="1">
@@ -5336,7 +5333,7 @@
         <v>121</v>
       </c>
       <c r="H6" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="97.8" customHeight="1">
@@ -5360,7 +5357,7 @@
         <v>127</v>
       </c>
       <c r="H7" s="45" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="112.8" customHeight="1">
@@ -5386,7 +5383,7 @@
         <v>133</v>
       </c>
       <c r="H8" s="47" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I8" s="46"/>
       <c r="J8" s="46"/>
@@ -5466,7 +5463,7 @@
         <v>139</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E3" s="15"/>
     </row>
@@ -5481,7 +5478,7 @@
         <v>142</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E4" s="21"/>
     </row>
@@ -5573,36 +5570,36 @@
         <v>157</v>
       </c>
       <c r="C4" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="E4" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="F4" s="42" t="s">
         <v>160</v>
-      </c>
-      <c r="F4" s="42" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="301.8" customHeight="1">
       <c r="A5" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="C5" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="D5" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="E5" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="F5" s="42" t="s">
         <v>166</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="406.8" customHeight="1">
@@ -5610,34 +5607,34 @@
         <v>156</v>
       </c>
       <c r="B6" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="D6" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="E6" s="42" t="s">
         <v>170</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>171</v>
       </c>
       <c r="F6" s="21"/>
     </row>
     <row r="7" spans="1:6" ht="409.6" customHeight="1">
       <c r="A7" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="C7" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="E7" s="42" t="s">
         <v>174</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>176</v>
       </c>
       <c r="F7" s="21"/>
     </row>
